--- a/Configs/GameConfig/Datas/weapon_text.xlsx
+++ b/Configs/GameConfig/Datas/weapon_text.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28bd056eb1f54890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95992685e0d341d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,12 +334,8 @@
       <x:c r="B1" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" t="str">
-        <x:v>txt</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>quality</x:v>
-      </x:c>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -348,12 +344,8 @@
       <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -368,1622 +360,1082 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>单字</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>品质</x:v>
-      </x:c>
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>短</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>弓</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>长</x:v>
-      </x:c>
-      <x:c r="D7" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>弓</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>铁</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>角</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>弓</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>射</x:v>
-      </x:c>
-      <x:c r="D12" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C13" t="str">
-        <x:v>雕</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>弓</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C15" t="str">
-        <x:v>铁</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>胎</x:v>
-      </x:c>
-      <x:c r="D16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17"/>
       <x:c r="B17" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>神</x:v>
-      </x:c>
-      <x:c r="D17" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>臂</x:v>
-      </x:c>
-      <x:c r="D18" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" t="str">
-        <x:v>霸</x:v>
-      </x:c>
-      <x:c r="D19" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>王</x:v>
-      </x:c>
-      <x:c r="D20" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C21" t="str">
-        <x:v>弓</x:v>
-      </x:c>
-      <x:c r="D21" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C22" t="str">
-        <x:v>落</x:v>
-      </x:c>
-      <x:c r="D22" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C23" t="str">
-        <x:v>日</x:v>
-      </x:c>
-      <x:c r="D23" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C24" t="str">
-        <x:v>诸</x:v>
-      </x:c>
-      <x:c r="D24" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C25" t="str">
-        <x:v>葛</x:v>
-      </x:c>
-      <x:c r="D25" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C26" t="str">
-        <x:v>连</x:v>
-      </x:c>
-      <x:c r="D26" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C27" t="str">
-        <x:v>弩</x:v>
-      </x:c>
-      <x:c r="D27" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C28" t="str">
-        <x:v>枪</x:v>
-      </x:c>
-      <x:c r="D28" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C29" t="str">
-        <x:v>枪</x:v>
-      </x:c>
-      <x:c r="D29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C30" t="str">
-        <x:v>大</x:v>
-      </x:c>
-      <x:c r="D30" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C31" t="str">
-        <x:v>戟</x:v>
-      </x:c>
-      <x:c r="D31" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C32" t="str">
-        <x:v>钩</x:v>
-      </x:c>
-      <x:c r="D32" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C33" t="str">
-        <x:v>镰</x:v>
-      </x:c>
-      <x:c r="D33" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C34" t="str">
-        <x:v>枪</x:v>
-      </x:c>
-      <x:c r="D34" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
       <x:c r="B35" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C35" t="str">
-        <x:v>点</x:v>
-      </x:c>
-      <x:c r="D35" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
       <x:c r="B36" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C36" t="str">
-        <x:v>钢</x:v>
-      </x:c>
-      <x:c r="D36" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37"/>
       <x:c r="B37" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C37" t="str">
-        <x:v>枪</x:v>
-      </x:c>
-      <x:c r="D37" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38"/>
       <x:c r="B38" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C38" t="str">
-        <x:v>梨</x:v>
-      </x:c>
-      <x:c r="D38" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39"/>
       <x:c r="B39" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C39" t="str">
-        <x:v>花</x:v>
-      </x:c>
-      <x:c r="D39" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40"/>
       <x:c r="B40" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C40" t="str">
-        <x:v>虎</x:v>
-      </x:c>
-      <x:c r="D40" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41"/>
       <x:c r="B41" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C41" t="str">
-        <x:v>头</x:v>
-      </x:c>
-      <x:c r="D41" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
       <x:c r="B42" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C42" t="str">
-        <x:v>湛</x:v>
-      </x:c>
-      <x:c r="D42" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43"/>
       <x:c r="B43" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C43" t="str">
-        <x:v>金</x:v>
-      </x:c>
-      <x:c r="D43" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
       <x:c r="B44" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C44" t="str">
-        <x:v>丈</x:v>
-      </x:c>
-      <x:c r="D44" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45"/>
       <x:c r="B45" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C45" t="str">
-        <x:v>八</x:v>
-      </x:c>
-      <x:c r="D45" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46"/>
       <x:c r="B46" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C46" t="str">
-        <x:v>蛇</x:v>
-      </x:c>
-      <x:c r="D46" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47"/>
       <x:c r="B47" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C47" t="str">
-        <x:v>矛</x:v>
-      </x:c>
-      <x:c r="D47" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48"/>
       <x:c r="B48" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C48" t="str">
-        <x:v>龙</x:v>
-      </x:c>
-      <x:c r="D48" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49"/>
       <x:c r="B49" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C49" t="str">
-        <x:v>胆</x:v>
-      </x:c>
-      <x:c r="D49" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50"/>
       <x:c r="B50" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C50" t="str">
-        <x:v>亮</x:v>
-      </x:c>
-      <x:c r="D50" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51"/>
       <x:c r="B51" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C51" t="str">
-        <x:v>银</x:v>
-      </x:c>
-      <x:c r="D51" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52"/>
       <x:c r="B52" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C52" t="str">
-        <x:v>枪</x:v>
-      </x:c>
-      <x:c r="D52" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53"/>
       <x:c r="B53" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C53" t="str">
-        <x:v>刀</x:v>
-      </x:c>
-      <x:c r="D53" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54"/>
       <x:c r="B54" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C54" t="str">
-        <x:v>刀</x:v>
-      </x:c>
-      <x:c r="D54" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55"/>
       <x:c r="B55" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C55" t="str">
-        <x:v>狼</x:v>
-      </x:c>
-      <x:c r="D55" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56"/>
       <x:c r="B56" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C56" t="str">
-        <x:v>牙</x:v>
-      </x:c>
-      <x:c r="D56" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57"/>
       <x:c r="B57" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C57" t="str">
-        <x:v>棒</x:v>
-      </x:c>
-      <x:c r="D57" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58"/>
       <x:c r="B58" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C58" t="str">
-        <x:v>三</x:v>
-      </x:c>
-      <x:c r="D58" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59"/>
       <x:c r="B59" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C59" t="str">
-        <x:v>尖</x:v>
-      </x:c>
-      <x:c r="D59" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60"/>
       <x:c r="B60" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C60" t="str">
-        <x:v>刀</x:v>
-      </x:c>
-      <x:c r="D60" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61"/>
       <x:c r="B61" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C61" t="str">
-        <x:v>铁</x:v>
-      </x:c>
-      <x:c r="D61" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C61"/>
+      <x:c r="D61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62"/>
       <x:c r="B62" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C62" t="str">
-        <x:v>蒺</x:v>
-      </x:c>
-      <x:c r="D62" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C62"/>
+      <x:c r="D62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63"/>
       <x:c r="B63" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C63" t="str">
-        <x:v>藜</x:v>
-      </x:c>
-      <x:c r="D63" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C63"/>
+      <x:c r="D63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64"/>
       <x:c r="B64" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C64" t="str">
-        <x:v>骨</x:v>
-      </x:c>
-      <x:c r="D64" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65"/>
       <x:c r="B65" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C65" t="str">
-        <x:v>朵</x:v>
-      </x:c>
-      <x:c r="D65" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66"/>
       <x:c r="B66" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C66" t="str">
-        <x:v>古</x:v>
-      </x:c>
-      <x:c r="D66" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67"/>
       <x:c r="B67" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C67" t="str">
-        <x:v>锭</x:v>
-      </x:c>
-      <x:c r="D67" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68"/>
       <x:c r="B68" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C68" t="str">
-        <x:v>刀</x:v>
-      </x:c>
-      <x:c r="D68" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69"/>
       <x:c r="B69" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C69" t="str">
-        <x:v>啸</x:v>
-      </x:c>
-      <x:c r="D69" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70"/>
       <x:c r="B70" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C70" t="str">
-        <x:v>战</x:v>
-      </x:c>
-      <x:c r="D70" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71"/>
       <x:c r="B71" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C71" t="str">
-        <x:v>七</x:v>
-      </x:c>
-      <x:c r="D71" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72"/>
       <x:c r="B72" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C72" t="str">
-        <x:v>星</x:v>
-      </x:c>
-      <x:c r="D72" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C72"/>
+      <x:c r="D72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73"/>
       <x:c r="B73" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C73" t="str">
-        <x:v>青</x:v>
-      </x:c>
-      <x:c r="D73" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C73"/>
+      <x:c r="D73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74"/>
       <x:c r="B74" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C74" t="str">
-        <x:v>偃</x:v>
-      </x:c>
-      <x:c r="D74" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C74"/>
+      <x:c r="D74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75"/>
       <x:c r="B75" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C75" t="str">
-        <x:v>月</x:v>
-      </x:c>
-      <x:c r="D75" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76"/>
       <x:c r="B76" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C76" t="str">
-        <x:v>刀</x:v>
-      </x:c>
-      <x:c r="D76" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77"/>
       <x:c r="B77" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C77" t="str">
-        <x:v>方</x:v>
-      </x:c>
-      <x:c r="D77" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78"/>
       <x:c r="B78" t="n">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C78" t="str">
-        <x:v>天</x:v>
-      </x:c>
-      <x:c r="D78" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79"/>
       <x:c r="B79" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C79" t="str">
-        <x:v>画</x:v>
-      </x:c>
-      <x:c r="D79" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80"/>
       <x:c r="B80" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C80" t="str">
-        <x:v>戟</x:v>
-      </x:c>
-      <x:c r="D80" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81"/>
       <x:c r="B81" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C81" t="str">
-        <x:v>剑</x:v>
-      </x:c>
-      <x:c r="D81" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82"/>
       <x:c r="B82" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C82" t="str">
-        <x:v>剑</x:v>
-      </x:c>
-      <x:c r="D82" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83"/>
       <x:c r="B83" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C83" t="str">
-        <x:v>巨</x:v>
-      </x:c>
-      <x:c r="D83" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84"/>
       <x:c r="B84" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C84" t="str">
-        <x:v>阙</x:v>
-      </x:c>
-      <x:c r="D84" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85"/>
       <x:c r="B85" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C85" t="str">
-        <x:v>剑</x:v>
-      </x:c>
-      <x:c r="D85" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86"/>
       <x:c r="B86" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C86" t="str">
-        <x:v>龙</x:v>
-      </x:c>
-      <x:c r="D86" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87"/>
       <x:c r="B87" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C87" t="str">
-        <x:v>泉</x:v>
-      </x:c>
-      <x:c r="D87" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88"/>
       <x:c r="B88" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C88" t="str">
-        <x:v>龙</x:v>
-      </x:c>
-      <x:c r="D88" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89"/>
       <x:c r="B89" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C89" t="str">
-        <x:v>渊</x:v>
-      </x:c>
-      <x:c r="D89" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90"/>
       <x:c r="B90" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C90" t="str">
-        <x:v>剑</x:v>
-      </x:c>
-      <x:c r="D90" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91"/>
       <x:c r="B91" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C91" t="str">
-        <x:v>双</x:v>
-      </x:c>
-      <x:c r="D91" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92"/>
       <x:c r="B92" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C92" t="str">
-        <x:v>股</x:v>
-      </x:c>
-      <x:c r="D92" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93"/>
       <x:c r="B93" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C93" t="str">
-        <x:v>青</x:v>
-      </x:c>
-      <x:c r="D93" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94"/>
       <x:c r="B94" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C94" t="str">
-        <x:v>釭</x:v>
-      </x:c>
-      <x:c r="D94" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C94"/>
+      <x:c r="D94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95"/>
       <x:c r="B95" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C95" t="str">
-        <x:v>倚</x:v>
-      </x:c>
-      <x:c r="D95" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C95"/>
+      <x:c r="D95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96"/>
       <x:c r="B96" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C96" t="str">
-        <x:v>剑</x:v>
-      </x:c>
-      <x:c r="D96" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C96"/>
+      <x:c r="D96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97"/>
       <x:c r="B97" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C97" t="str">
-        <x:v>莫</x:v>
-      </x:c>
-      <x:c r="D97" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C97"/>
+      <x:c r="D97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98"/>
       <x:c r="B98" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C98" t="str">
-        <x:v>邪</x:v>
-      </x:c>
-      <x:c r="D98" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99"/>
       <x:c r="B99" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C99" t="str">
-        <x:v>干</x:v>
-      </x:c>
-      <x:c r="D99" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100"/>
       <x:c r="B100" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C100" t="str">
-        <x:v>将</x:v>
-      </x:c>
-      <x:c r="D100" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101"/>
       <x:c r="B101" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C101" t="str">
-        <x:v>轩</x:v>
-      </x:c>
-      <x:c r="D101" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102"/>
       <x:c r="B102" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C102" t="str">
-        <x:v>辕</x:v>
-      </x:c>
-      <x:c r="D102" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103"/>
       <x:c r="B103" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C103" t="str">
-        <x:v>尉</x:v>
-      </x:c>
-      <x:c r="D103" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104"/>
       <x:c r="B104" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C104" t="str">
-        <x:v>缭</x:v>
-      </x:c>
-      <x:c r="D104" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105"/>
       <x:c r="B105" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C105" t="str">
-        <x:v>子</x:v>
-      </x:c>
-      <x:c r="D105" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106"/>
       <x:c r="B106" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C106" t="str">
-        <x:v>墨</x:v>
-      </x:c>
-      <x:c r="D106" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107"/>
       <x:c r="B107" t="n">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C107" t="str">
-        <x:v>吴</x:v>
-      </x:c>
-      <x:c r="D107" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108"/>
       <x:c r="B108" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C108" t="str">
-        <x:v>太</x:v>
-      </x:c>
-      <x:c r="D108" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109"/>
       <x:c r="B109" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C109" t="str">
-        <x:v>白</x:v>
-      </x:c>
-      <x:c r="D109" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110"/>
       <x:c r="B110" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C110" t="str">
-        <x:v>阴</x:v>
-      </x:c>
-      <x:c r="D110" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111"/>
       <x:c r="B111" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C111" t="str">
-        <x:v>经</x:v>
-      </x:c>
-      <x:c r="D111" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112"/>
       <x:c r="B112" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C112" t="str">
-        <x:v>黄</x:v>
-      </x:c>
-      <x:c r="D112" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113"/>
       <x:c r="B113" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="C113" t="str">
-        <x:v>石</x:v>
-      </x:c>
-      <x:c r="D113" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114"/>
       <x:c r="B114" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="C114" t="str">
-        <x:v>公</x:v>
-      </x:c>
-      <x:c r="D114" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115"/>
       <x:c r="B115" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C115" t="str">
-        <x:v>记</x:v>
-      </x:c>
-      <x:c r="D115" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116"/>
       <x:c r="B116" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C116" t="str">
-        <x:v>孙</x:v>
-      </x:c>
-      <x:c r="D116" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117"/>
       <x:c r="B117" t="n">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C117" t="str">
-        <x:v>膑</x:v>
-      </x:c>
-      <x:c r="D117" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118"/>
       <x:c r="B118" t="n">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C118" t="str">
-        <x:v>兵</x:v>
-      </x:c>
-      <x:c r="D118" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119"/>
       <x:c r="B119" t="n">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C119" t="str">
-        <x:v>法</x:v>
-      </x:c>
-      <x:c r="D119" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C119"/>
+      <x:c r="D119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120"/>
       <x:c r="B120" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C120" t="str">
-        <x:v>太</x:v>
-      </x:c>
-      <x:c r="D120" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C120"/>
+      <x:c r="D120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121"/>
       <x:c r="B121" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="C121" t="str">
-        <x:v>公</x:v>
-      </x:c>
-      <x:c r="D121" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C121"/>
+      <x:c r="D121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122"/>
       <x:c r="B122" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C122" t="str">
-        <x:v>兵</x:v>
-      </x:c>
-      <x:c r="D122" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C122"/>
+      <x:c r="D122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123"/>
       <x:c r="B123" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C123" t="str">
-        <x:v>法</x:v>
-      </x:c>
-      <x:c r="D123" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C123"/>
+      <x:c r="D123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124"/>
       <x:c r="B124" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C124" t="str">
-        <x:v>鬼</x:v>
-      </x:c>
-      <x:c r="D124" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C124"/>
+      <x:c r="D124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125"/>
       <x:c r="B125" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C125" t="str">
-        <x:v>谷</x:v>
-      </x:c>
-      <x:c r="D125" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126"/>
       <x:c r="B126" t="n">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C126" t="str">
-        <x:v>子</x:v>
-      </x:c>
-      <x:c r="D126" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C126"/>
+      <x:c r="D126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127"/>
       <x:c r="B127" t="n">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C127" t="str">
-        <x:v>奇</x:v>
-      </x:c>
-      <x:c r="D127" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128"/>
       <x:c r="B128" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C128" t="str">
-        <x:v>门</x:v>
-      </x:c>
-      <x:c r="D128" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129"/>
       <x:c r="B129" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C129" t="str">
-        <x:v>遁</x:v>
-      </x:c>
-      <x:c r="D129" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C129"/>
+      <x:c r="D129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130"/>
       <x:c r="B130" t="n">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C130" t="str">
-        <x:v>甲</x:v>
-      </x:c>
-      <x:c r="D130" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C130"/>
+      <x:c r="D130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131"/>
       <x:c r="B131" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="C131" t="str">
-        <x:v>三</x:v>
-      </x:c>
-      <x:c r="D131" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C131"/>
+      <x:c r="D131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132"/>
       <x:c r="B132" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="C132" t="str">
-        <x:v>十</x:v>
-      </x:c>
-      <x:c r="D132" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C132"/>
+      <x:c r="D132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133"/>
       <x:c r="B133" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C133" t="str">
-        <x:v>六</x:v>
-      </x:c>
-      <x:c r="D133" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C133"/>
+      <x:c r="D133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134"/>
       <x:c r="B134" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C134" t="str">
-        <x:v>计</x:v>
-      </x:c>
-      <x:c r="D134" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C134"/>
+      <x:c r="D134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135"/>
       <x:c r="B135" t="n">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="C135" t="str">
-        <x:v>孙</x:v>
-      </x:c>
-      <x:c r="D135" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C135"/>
+      <x:c r="D135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136"/>
       <x:c r="B136" t="n">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C136" t="str">
-        <x:v>子</x:v>
-      </x:c>
-      <x:c r="D136" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C136"/>
+      <x:c r="D136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137"/>
       <x:c r="B137" t="n">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C137" t="str">
-        <x:v>兵</x:v>
-      </x:c>
-      <x:c r="D137" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C137"/>
+      <x:c r="D137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138"/>
       <x:c r="B138" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="C138" t="str">
-        <x:v>法</x:v>
-      </x:c>
-      <x:c r="D138" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C138"/>
+      <x:c r="D138"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
